--- a/files/九龙-长沙湾-家壹.xlsx
+++ b/files/九龙-长沙湾-家壹.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家壹 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家壹" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,19 +213,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,10 +231,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -598,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -9877,153 +9915,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>家壹 - 家壹 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>家壹 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>200 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>193 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,113万
+$1113万
 $23,232/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $657万
@@ -10031,7 +10069,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $659万
@@ -10039,7 +10077,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $666万
@@ -10047,7 +10085,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $687万
@@ -10055,7 +10093,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $521万
@@ -10063,7 +10101,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $583万
@@ -10071,7 +10109,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $579万
@@ -10080,21 +10118,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,073万
+$1073万
 $22,405/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $645万
@@ -10102,7 +10140,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $635万
@@ -10110,7 +10148,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $642万
@@ -10118,7 +10156,7 @@
 (19年-09月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $657万
@@ -10126,7 +10164,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $518万
@@ -10134,7 +10172,7 @@
 (19年-09月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $562万
@@ -10142,7 +10180,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $562万
@@ -10151,21 +10189,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,053万
+$1053万
 $21,976/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $632万
@@ -10173,7 +10211,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $630万
@@ -10181,7 +10219,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $650万
@@ -10189,7 +10227,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $652万
@@ -10197,7 +10235,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $520万
@@ -10205,7 +10243,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $558万
@@ -10213,7 +10251,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $557万
@@ -10222,21 +10260,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,134万
+$1134万
 $23,685/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $636万
@@ -10244,7 +10282,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $624万
@@ -10252,7 +10290,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $624万
@@ -10260,7 +10298,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $653万
@@ -10268,7 +10306,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $504万
@@ -10276,7 +10314,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $559万
@@ -10284,7 +10322,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $547万
@@ -10293,21 +10331,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,125万
+$1125万
 $23,480/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $630万
@@ -10315,7 +10353,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $626万
@@ -10323,7 +10361,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $626万
@@ -10331,7 +10369,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $648万
@@ -10339,7 +10377,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $500万
@@ -10347,7 +10385,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $576万
@@ -10355,7 +10393,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $551万
@@ -10364,21 +10402,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,029万
+$1029万
 $21,475/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $620万
@@ -10386,7 +10424,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $615万
@@ -10394,7 +10432,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $615万
@@ -10402,7 +10440,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $637万
@@ -10410,7 +10448,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $513万
@@ -10418,7 +10456,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $532万
@@ -10426,7 +10464,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $554万
@@ -10435,21 +10473,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,184万
+$1184万
 $24,729/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $637万
@@ -10457,7 +10495,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $612万
@@ -10465,7 +10503,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $598万
@@ -10473,7 +10511,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $634万
@@ -10481,7 +10519,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $500万
@@ -10489,7 +10527,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $535万
@@ -10497,7 +10535,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $562万
@@ -10506,21 +10544,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,105万
+$1105万
 $23,071/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $614万
@@ -10528,7 +10566,7 @@
 (19年-05月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $608万
@@ -10536,7 +10574,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $601万
@@ -10544,7 +10582,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $630万
@@ -10552,7 +10590,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $498万
@@ -10560,7 +10598,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $526万
@@ -10568,7 +10606,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $536万
@@ -10577,21 +10615,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,022万
+$1022万
 $21,330/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $630万
@@ -10599,7 +10637,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $611万
@@ -10607,7 +10645,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $597万
@@ -10615,7 +10653,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $647万
@@ -10623,7 +10661,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $490万
@@ -10631,7 +10669,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $534万
@@ -10639,7 +10677,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $538万
@@ -10648,21 +10686,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,005万
+$1005万
 $20,974/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $627万
@@ -10670,7 +10708,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $621万
@@ -10678,7 +10716,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $587万
@@ -10686,7 +10724,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $623万
@@ -10694,7 +10732,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $492万
@@ -10702,7 +10740,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $531万
@@ -10710,7 +10748,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $535万
@@ -10719,21 +10757,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,010万
+$1010万
 $21,075/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $656万
@@ -10741,7 +10779,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $597万
@@ -10749,7 +10787,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $584万
@@ -10757,7 +10795,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $639万
@@ -10765,7 +10803,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $484万
@@ -10773,7 +10811,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $528万
@@ -10781,7 +10819,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $527万
@@ -10790,21 +10828,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,003万
+$1003万
 $20,949/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $602万
@@ -10812,7 +10850,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $594万
@@ -10820,7 +10858,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $586万
@@ -10828,7 +10866,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $629万
@@ -10836,7 +10874,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $483万
@@ -10844,7 +10882,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $514万
@@ -10852,7 +10890,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $529万
@@ -10861,21 +10899,21 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
-$1,002万
+$1002万
 $20,922/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $621万
@@ -10883,7 +10921,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $590万
@@ -10891,7 +10929,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $589万
@@ -10899,7 +10937,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $598万
@@ -10907,7 +10945,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $525万
@@ -10915,7 +10953,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $510万
@@ -10923,7 +10961,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $526万
@@ -10932,13 +10970,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $985万
@@ -10946,7 +10984,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $646万
@@ -10954,7 +10992,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $587万
@@ -10962,7 +11000,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $573万
@@ -10970,7 +11008,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $601万
@@ -10978,7 +11016,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $481万
@@ -10986,7 +11024,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $513万
@@ -10994,7 +11032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $517万
@@ -11003,13 +11041,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $979万
@@ -11017,7 +11055,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $598万
@@ -11025,7 +11063,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $583万
@@ -11033,7 +11071,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $570万
@@ -11041,7 +11079,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $591万
@@ -11049,7 +11087,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $488万
@@ -11057,7 +11095,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $504万
@@ -11065,7 +11103,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $520万
@@ -11074,13 +11112,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $984万
@@ -11088,7 +11126,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $595万
@@ -11096,7 +11134,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $579万
@@ -11104,7 +11142,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $566万
@@ -11112,7 +11150,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $587万
@@ -11120,7 +11158,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $475万
@@ -11128,7 +11166,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $512万
@@ -11136,7 +11174,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $528万
@@ -11145,13 +11183,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $978万
@@ -11159,7 +11197,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $598万
@@ -11167,7 +11205,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $576万
@@ -11175,7 +11213,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $569万
@@ -11183,7 +11221,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $595万
@@ -11191,7 +11229,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $469万
@@ -11199,7 +11237,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $498万
@@ -11207,7 +11245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $508万
@@ -11216,13 +11254,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $961万
@@ -11230,7 +11268,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $588万
@@ -11238,7 +11276,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $591万
@@ -11246,7 +11284,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $577万
@@ -11254,7 +11292,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $627万
@@ -11262,7 +11300,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $464万
@@ -11270,7 +11308,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $495万
@@ -11278,7 +11316,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $505万
@@ -11287,13 +11325,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $966万
@@ -11301,7 +11339,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $598万
@@ -11309,7 +11347,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $575万
@@ -11317,7 +11355,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $574万
@@ -11325,7 +11363,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $573万
@@ -11333,7 +11371,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $471万
@@ -11341,7 +11379,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $502万
@@ -11349,7 +11387,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $502万
@@ -11358,13 +11396,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $941万
@@ -11372,7 +11410,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $582万
@@ -11380,7 +11418,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $571万
@@ -11388,7 +11426,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $558万
@@ -11396,7 +11434,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $570万
@@ -11404,7 +11442,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $458万
@@ -11412,7 +11450,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $499万
@@ -11420,7 +11458,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $504万
@@ -11429,13 +11467,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $925万
@@ -11443,7 +11481,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $579万
@@ -11451,7 +11489,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $624万
@@ -11459,7 +11497,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $549万
@@ -11467,7 +11505,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $566万
@@ -11475,7 +11513,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $455万
@@ -11483,7 +11521,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $554万
@@ -11491,7 +11529,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $534万
@@ -11500,13 +11538,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $926万
@@ -11514,7 +11552,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $574万
@@ -11522,7 +11560,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $556万
@@ -11530,7 +11568,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $549万
@@ -11538,7 +11576,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $567万
@@ -11546,7 +11584,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $451万
@@ -11554,7 +11592,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $482万
@@ -11562,7 +11600,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $493万
@@ -11571,13 +11609,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $907万
@@ -11585,7 +11623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $570万
@@ -11593,7 +11631,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $551万
@@ -11601,7 +11639,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $550万
@@ -11609,7 +11647,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $556万
@@ -11617,7 +11655,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 220呎 (开放式)
 $447万
@@ -11625,7 +11663,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $478万
@@ -11633,7 +11671,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $488万
@@ -11642,13 +11680,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 479呎 (2房)
 $898万
@@ -11656,7 +11694,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
 $565万
@@ -11664,7 +11702,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $545万
@@ -11672,7 +11710,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 277呎 (1房)
 $598万
@@ -11680,7 +11718,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
 $550万
@@ -11688,7 +11726,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 221呎 (开放式)
 $443万
@@ -11696,7 +11734,7 @@
 (19年-04月)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 238呎 (开放式)
 $476万
@@ -11704,7 +11742,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 226呎 (开放式)
 $487万
@@ -11713,21 +11751,21 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 458呎 (2房)
-$1,261万
+$1261万
 $27,538/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 244呎 (1房)
 $543万
@@ -11735,7 +11773,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 255呎 (1房)
 $546万
@@ -11743,7 +11781,7 @@
 (19年-12月)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $546万
@@ -11751,7 +11789,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $704万
@@ -11759,7 +11797,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 199呎 (开放式)
 $646万
@@ -11767,7 +11805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 216呎 (开放式)
 $630万
@@ -11775,7 +11813,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 205呎 (开放式)
 $764万
@@ -11786,7 +11824,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
